--- a/review/exports/Welsh-LDS-Possible-Branches.xlsx
+++ b/review/exports/Welsh-LDS-Possible-Branches.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rcdd511fed190429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="R2308bd3b3af04773"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -801,7 +801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbc085619f3b4eee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a18e825d664a1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>